--- a/data.mn/public/datasets/household-income-by-location.xlsx
+++ b/data.mn/public/datasets/household-income-by-location.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="English" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mongolian" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Mongolian" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -435,17 +423,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -1163,7 +1151,7 @@
         <v>2024</v>
       </c>
       <c r="C56" t="n">
-        <v>2069149</v>
+        <v>2068755</v>
       </c>
     </row>
     <row r="57">
@@ -1176,7 +1164,33 @@
         <v>2024</v>
       </c>
       <c r="C57" t="n">
-        <v>2803740</v>
+        <v>2811463</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2521581</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C59" t="n">
+        <v>3286767</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1199,17 +1213,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>байршил</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>он</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>утга</t>
         </is>
@@ -1927,7 +1941,7 @@
         <v>2024</v>
       </c>
       <c r="C56" t="n">
-        <v>2803740</v>
+        <v>2811463</v>
       </c>
     </row>
     <row r="57">
@@ -1940,7 +1954,33 @@
         <v>2024</v>
       </c>
       <c r="C57" t="n">
-        <v>2069149</v>
+        <v>2068755</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Хот</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3286767</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Хөдөө</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C59" t="n">
+        <v>2521581</v>
       </c>
     </row>
   </sheetData>
